--- a/AAII_Financials/Yearly/MGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MGN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="92">
   <si>
     <t>MGN</t>
   </si>
@@ -1594,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>15400</v>
+        <v>7200</v>
       </c>
       <c r="E42" s="3">
         <v>5100</v>
@@ -1683,8 +1683,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>8200</v>
       </c>
       <c r="E45" s="3">
         <v>2500</v>
@@ -2072,7 +2072,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6700</v>
+        <v>10300</v>
       </c>
       <c r="E59" s="3">
         <v>7100</v>
